--- a/Assessment Questions/CDA/PYF-110/PYTHON BASICS/Installation of python and IDE/Installation.xlsx
+++ b/Assessment Questions/CDA/PYF-110/PYTHON BASICS/Installation of python and IDE/Installation.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Installation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
